--- a/Employee_Reports_wi48/Mohamed Faris Mohamed Naleem Q0519.xlsx
+++ b/Employee_Reports_wi48/Mohamed Faris Mohamed Naleem Q0519.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -704,11 +704,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
